--- a/data/Gen-Elections.xlsx
+++ b/data/Gen-Elections.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e46a4301436fbcaf/Kalyan/KK-Python/Kalyan-Jupyter-Notebooks/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="864" documentId="8_{4C723204-91D3-914E-9519-B4FDAEE31F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DD48AA9-097E-BB48-9B22-0766A8BC354D}"/>
+  <xr:revisionPtr revIDLastSave="865" documentId="8_{4C723204-91D3-914E-9519-B4FDAEE31F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79873623-2A71-8C45-A11F-20BFE7D66B64}"/>
   <bookViews>
-    <workbookView xWindow="320" yWindow="500" windowWidth="28040" windowHeight="15520" activeTab="4" xr2:uid="{CF7E420C-519C-EF4C-A53D-F0FF9AECEAB4}"/>
+    <workbookView xWindow="320" yWindow="740" windowWidth="28040" windowHeight="15520" activeTab="4" xr2:uid="{CF7E420C-519C-EF4C-A53D-F0FF9AECEAB4}"/>
   </bookViews>
   <sheets>
     <sheet name="Poll-Schedule" sheetId="1" r:id="rId1"/>
-    <sheet name="Poll-Date" sheetId="6" r:id="rId2"/>
+    <sheet name="Poll-Date-2024" sheetId="6" r:id="rId2"/>
     <sheet name="PC-Poll-Schedule" sheetId="2" r:id="rId3"/>
     <sheet name="AC-Poll-Schedule" sheetId="3" r:id="rId4"/>
     <sheet name="PC-Sch-2024" sheetId="8" r:id="rId5"/>
@@ -4511,35 +4511,74 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="15" fontId="12" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="8"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="8"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="8"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="8"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
@@ -4586,74 +4625,35 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
     </xf>
-    <xf numFmtId="15" fontId="12" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="15" fontId="12" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="8"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="8"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="8"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="8"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="6"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5006,31 +5006,31 @@
     <row r="1" spans="1:11" ht="21" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="4"/>
-      <c r="C1" s="113" t="s">
+      <c r="C1" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
-      <c r="I1" s="114"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="115"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:11" ht="37" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="5"/>
-      <c r="C2" s="113" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="115"/>
-      <c r="E2" s="116" t="s">
+      <c r="C2" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="78"/>
+      <c r="E2" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="117"/>
+      <c r="F2" s="80"/>
       <c r="G2" s="8" t="s">
         <v>6</v>
       </c>
@@ -5054,14 +5054,14 @@
       <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="118" t="s">
+      <c r="C3" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="119"/>
-      <c r="E3" s="120" t="s">
+      <c r="D3" s="82"/>
+      <c r="E3" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="121"/>
+      <c r="F3" s="84"/>
       <c r="G3" s="9" t="s">
         <v>13</v>
       </c>
@@ -5101,7 +5101,7 @@
     </row>
     <row r="5" spans="1:11" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13"/>
-      <c r="B5" s="103" t="s">
+      <c r="B5" s="74" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="15">
@@ -5136,7 +5136,7 @@
       <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="104"/>
+      <c r="B6" s="75"/>
       <c r="C6" s="16" t="s">
         <v>23</v>
       </c>
@@ -5167,7 +5167,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="24"/>
-      <c r="B7" s="103" t="s">
+      <c r="B7" s="74" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="25">
@@ -5202,7 +5202,7 @@
       <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="104"/>
+      <c r="B8" s="75"/>
       <c r="C8" s="26" t="s">
         <v>25</v>
       </c>
@@ -5233,7 +5233,7 @@
     </row>
     <row r="9" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="36"/>
-      <c r="B9" s="103" t="s">
+      <c r="B9" s="74" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="15">
@@ -5268,7 +5268,7 @@
       <c r="A10" s="14">
         <v>3</v>
       </c>
-      <c r="B10" s="104"/>
+      <c r="B10" s="75"/>
       <c r="C10" s="20" t="s">
         <v>25</v>
       </c>
@@ -5299,7 +5299,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="40"/>
-      <c r="B11" s="103" t="s">
+      <c r="B11" s="74" t="s">
         <v>31</v>
       </c>
       <c r="C11" s="25">
@@ -5334,7 +5334,7 @@
       <c r="A12" s="14">
         <v>4</v>
       </c>
-      <c r="B12" s="104"/>
+      <c r="B12" s="75"/>
       <c r="C12" s="41" t="s">
         <v>26</v>
       </c>
@@ -5365,7 +5365,7 @@
     </row>
     <row r="13" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="45"/>
-      <c r="B13" s="103" t="s">
+      <c r="B13" s="74" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="15">
@@ -5400,7 +5400,7 @@
       <c r="A14" s="14">
         <v>5</v>
       </c>
-      <c r="B14" s="104"/>
+      <c r="B14" s="75"/>
       <c r="C14" s="16" t="s">
         <v>23</v>
       </c>
@@ -5432,14 +5432,14 @@
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="36"/>
       <c r="B15" s="47"/>
-      <c r="C15" s="99">
+      <c r="C15" s="85">
         <v>45401</v>
       </c>
-      <c r="D15" s="100"/>
-      <c r="E15" s="99">
+      <c r="D15" s="86"/>
+      <c r="E15" s="85">
         <v>45408</v>
       </c>
-      <c r="F15" s="100"/>
+      <c r="F15" s="86"/>
       <c r="G15" s="31">
         <v>45419</v>
       </c>
@@ -5463,14 +5463,14 @@
       <c r="B16" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="101" t="s">
+      <c r="C16" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="102"/>
-      <c r="E16" s="101" t="s">
+      <c r="D16" s="88"/>
+      <c r="E16" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="102"/>
+      <c r="F16" s="88"/>
       <c r="G16" s="32" t="s">
         <v>29</v>
       </c>
@@ -5489,30 +5489,30 @@
     </row>
     <row r="17" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="49"/>
-      <c r="B17" s="103" t="s">
+      <c r="B17" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="105" t="s">
+      <c r="C17" s="89" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="106"/>
-      <c r="E17" s="109" t="s">
+      <c r="D17" s="90"/>
+      <c r="E17" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="F17" s="110"/>
-      <c r="G17" s="84" t="s">
+      <c r="F17" s="94"/>
+      <c r="G17" s="97" t="s">
         <v>35</v>
       </c>
-      <c r="H17" s="84" t="s">
+      <c r="H17" s="97" t="s">
         <v>35</v>
       </c>
-      <c r="I17" s="84" t="s">
+      <c r="I17" s="97" t="s">
         <v>35</v>
       </c>
-      <c r="J17" s="86" t="s">
+      <c r="J17" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="K17" s="86" t="s">
+      <c r="K17" s="99" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5520,26 +5520,26 @@
       <c r="A18" s="14">
         <v>7</v>
       </c>
-      <c r="B18" s="104"/>
-      <c r="C18" s="107"/>
-      <c r="D18" s="108"/>
-      <c r="E18" s="111"/>
-      <c r="F18" s="112"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="85"/>
-      <c r="I18" s="85"/>
-      <c r="J18" s="87"/>
-      <c r="K18" s="87"/>
+      <c r="B18" s="75"/>
+      <c r="C18" s="91"/>
+      <c r="D18" s="92"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="96"/>
+      <c r="G18" s="98"/>
+      <c r="H18" s="98"/>
+      <c r="I18" s="98"/>
+      <c r="J18" s="100"/>
+      <c r="K18" s="100"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="40"/>
-      <c r="B19" s="88" t="s">
+      <c r="B19" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="91"/>
-      <c r="D19" s="92"/>
-      <c r="E19" s="91"/>
-      <c r="F19" s="92"/>
+      <c r="C19" s="104"/>
+      <c r="D19" s="105"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="105"/>
       <c r="G19" s="51"/>
       <c r="H19" s="51"/>
       <c r="I19" s="51"/>
@@ -5548,15 +5548,15 @@
     </row>
     <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.2">
       <c r="A20" s="50"/>
-      <c r="B20" s="89"/>
-      <c r="C20" s="93" t="s">
+      <c r="B20" s="102"/>
+      <c r="C20" s="106" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="94"/>
-      <c r="E20" s="97" t="s">
+      <c r="D20" s="107"/>
+      <c r="E20" s="110" t="s">
         <v>37</v>
       </c>
-      <c r="F20" s="98"/>
+      <c r="F20" s="111"/>
       <c r="G20" s="52" t="s">
         <v>37</v>
       </c>
@@ -5577,11 +5577,11 @@
       <c r="A21" s="14">
         <v>8</v>
       </c>
-      <c r="B21" s="90"/>
-      <c r="C21" s="95"/>
-      <c r="D21" s="96"/>
-      <c r="E21" s="95"/>
-      <c r="F21" s="96"/>
+      <c r="B21" s="103"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="109"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="109"/>
       <c r="G21" s="53"/>
       <c r="H21" s="53"/>
       <c r="I21" s="53"/>
@@ -5593,14 +5593,14 @@
       <c r="B22" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="74">
+      <c r="C22" s="112">
         <v>102</v>
       </c>
-      <c r="D22" s="75"/>
-      <c r="E22" s="74">
+      <c r="D22" s="113"/>
+      <c r="E22" s="112">
         <v>89</v>
       </c>
-      <c r="F22" s="75"/>
+      <c r="F22" s="113"/>
       <c r="G22" s="56">
         <v>94</v>
       </c>
@@ -5618,14 +5618,14 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="76"/>
-      <c r="B23" s="78" t="s">
+      <c r="A23" s="114"/>
+      <c r="B23" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="80"/>
-      <c r="D23" s="81"/>
-      <c r="E23" s="80"/>
-      <c r="F23" s="81"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="119"/>
       <c r="G23" s="57"/>
       <c r="H23" s="57"/>
       <c r="I23" s="57"/>
@@ -5633,16 +5633,16 @@
       <c r="K23" s="57"/>
     </row>
     <row r="24" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="77"/>
-      <c r="B24" s="79"/>
-      <c r="C24" s="82">
+      <c r="A24" s="115"/>
+      <c r="B24" s="117"/>
+      <c r="C24" s="120">
         <v>21</v>
       </c>
-      <c r="D24" s="83"/>
-      <c r="E24" s="82">
+      <c r="D24" s="121"/>
+      <c r="E24" s="120">
         <v>13</v>
       </c>
-      <c r="F24" s="83"/>
+      <c r="F24" s="121"/>
       <c r="G24" s="56">
         <v>12</v>
       </c>
@@ -5661,23 +5661,14 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:D18"/>
-    <mergeCell ref="E17:F18"/>
-    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="H17:H18"/>
     <mergeCell ref="I17:I18"/>
     <mergeCell ref="J17:J18"/>
@@ -5690,14 +5681,23 @@
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="G17:G18"/>
     <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="E17:F18"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
